--- a/content/post/drafts/season-prediction/men_simple-model-tests-r2.xlsx
+++ b/content/post/drafts/season-prediction/men_simple-model-tests-r2.xlsx
@@ -610,25 +610,25 @@
         <v>15</v>
       </c>
       <c r="B9" t="n">
-        <v>0.455651922555247</v>
+        <v>0.464617646859342</v>
       </c>
       <c r="C9" t="n">
-        <v>0.722273404738922</v>
+        <v>0.716969050545895</v>
       </c>
       <c r="D9" t="n">
-        <v>0.390452304860753</v>
+        <v>0.396347568109234</v>
       </c>
       <c r="E9" t="n">
-        <v>0.432666393586523</v>
+        <v>0.411611421797701</v>
       </c>
       <c r="F9" t="n">
-        <v>0.517524656839117</v>
+        <v>0.501037022845415</v>
       </c>
       <c r="G9" t="n">
-        <v>0.569180559050536</v>
+        <v>0.559295445473031</v>
       </c>
       <c r="H9" t="n">
-        <v>0.514624873605183</v>
+        <v>0.508313025938436</v>
       </c>
     </row>
     <row r="10">
